--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484558_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484558_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. GARCÍA BURGOS</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9005</v>
+        <v>2.9135</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9005</v>
+        <v>1.5477</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9005</v>
+        <v>0.4362</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6502</v>
+        <v>-1.4522</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2502</v>
+        <v>1.8884</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9005</v>
+        <v>0.9707</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6502</v>
+        <v>-0.3409</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2502</v>
+        <v>1.3116</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0.5345</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-1.1113</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.5768</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0.5552</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.2263</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0.7815</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.3833</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.1163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VIVES HURTADO</t>
+          <t>G. GARCÍA BURGOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6543</v>
+        <v>1.9005</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0266</v>
+        <v>1.9005</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3723</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3199</v>
+        <v>1.9005</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1738</v>
+        <v>0.6502</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4937</v>
+        <v>1.2502</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3336</v>
+        <v>1.9005</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8913</v>
+        <v>0.6502</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5577</v>
+        <v>1.2502</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6535</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7175</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9774</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5988</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6214</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3697</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>A. VIVES HURTADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2894</v>
+        <v>0.9952</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1465</v>
+        <v>1.3674</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1429</v>
+        <v>-0.3723</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4362</v>
+        <v>-0.3199</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4522</v>
+        <v>0.1738</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8884</v>
+        <v>-0.4937</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9707</v>
+        <v>0.3336</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3409</v>
+        <v>0.8913</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3116</v>
+        <v>-0.5577</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5345</v>
+        <v>-0.6535</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1113</v>
+        <v>-0.7175</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5768</v>
+        <v>0.064</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5656</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.1794</v>
+        <v>1.3183</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1749</v>
+        <v>1.9397</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0045</v>
+        <v>-0.6214</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3833</v>
+        <v>-0.3697</v>
       </c>
       <c r="W4" t="n">
-        <v>1.267</v>
+        <v>0.0104</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1163</v>
+        <v>-0.3801</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>J. CLIMENT GOMIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6964</v>
+        <v>-1.6611</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4634</v>
+        <v>-0.3497</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2329</v>
+        <v>-1.3114</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0053</v>
+        <v>-0.6308</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.034</v>
+        <v>-0.3938</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0286</v>
+        <v>-0.237</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.532</v>
+        <v>-0.1468</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.6571</v>
+        <v>0.4427</v>
       </c>
       <c r="L6" t="n">
-        <v>0.125</v>
+        <v>-0.5895</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4733</v>
+        <v>-0.484</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3769</v>
+        <v>-0.8365</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0964</v>
+        <v>0.3525</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3823</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>2.211</v>
+        <v>-0.3441</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5792</v>
+        <v>-0.2029</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3682</v>
+        <v>-0.1412</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4518</v>
+        <v>-1.969</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7738</v>
+        <v>-1.969</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.018</v>
+        <v>-1.905</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7625</v>
+        <v>-0.7486</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2555</v>
+        <v>-1.1564</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8164</v>
@@ -1000,13 +1000,13 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3012</v>
+        <v>-0.1882</v>
       </c>
       <c r="T7" t="n">
-        <v>0.402</v>
+        <v>0.4159</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7032</v>
+        <v>-0.6041</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6335</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>M. GONZALEZ MAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0298</v>
+        <v>-2.2144</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.565</v>
+        <v>-1.514</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5353</v>
+        <v>-0.7005</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7789</v>
+        <v>-1.7929</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7277</v>
+        <v>-0.2223</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0512</v>
+        <v>-1.5706</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3743</v>
+        <v>-1.2387</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1576</v>
+        <v>0.0433</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5319</v>
+        <v>-1.2821</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4047</v>
+        <v>-0.5541</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8854</v>
+        <v>-0.2656</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4807</v>
+        <v>-0.2885</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0158</v>
+        <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9053</v>
+        <v>-0.7881</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4744</v>
+        <v>-0.2753</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4309</v>
+        <v>-0.5128</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5068</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GONZALEZ MAS</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2144</v>
+        <v>-2.3102</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.514</v>
+        <v>-0.9114</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7005</v>
+        <v>-1.3988</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7929</v>
+        <v>-2.5331</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2223</v>
+        <v>-1.3023</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5706</v>
+        <v>-1.2308</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2387</v>
+        <v>-1.753</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0433</v>
+        <v>-0.5543</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2821</v>
+        <v>-1.1987</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5541</v>
+        <v>-0.7801</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2656</v>
+        <v>-0.748</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2885</v>
+        <v>-0.0321</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7881</v>
+        <v>0.3752</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2753</v>
+        <v>0.8416</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5128</v>
+        <v>-0.4664</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.702</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.702</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CLIMENT GOMIS</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,37 +1189,37 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3237</v>
+        <v>-2.7083</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7893</v>
+        <v>-1.0503</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5344</v>
+        <v>-1.6581</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6308</v>
+        <v>-2.3069</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3938</v>
+        <v>-2.7269</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.237</v>
+        <v>0.4199</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1468</v>
+        <v>-1.6947</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4427</v>
+        <v>-1.7622</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5895</v>
+        <v>0.0674</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.484</v>
+        <v>-0.6122</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8365</v>
+        <v>-0.9647</v>
       </c>
       <c r="O10" t="n">
         <v>0.3525</v>
@@ -1234,28 +1234,28 @@
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0067</v>
+        <v>-0.0371</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6425</v>
+        <v>0.6444</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3642</v>
+        <v>-0.6816</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.969</v>
+        <v>-1.6471</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.969</v>
+        <v>-1.6471</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6453</v>
+        <v>-2.9535</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.296</v>
+        <v>-4.142</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3493</v>
+        <v>1.1884</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5331</v>
+        <v>-0.7789</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3023</v>
+        <v>-0.7277</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2308</v>
+        <v>-0.0512</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.753</v>
+        <v>-0.3743</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5543</v>
+        <v>0.1576</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1987</v>
+        <v>-0.5319</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7801</v>
+        <v>-0.4047</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.748</v>
+        <v>-0.8854</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0321</v>
+        <v>0.4807</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5498</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0401</v>
+        <v>-0.0185</v>
       </c>
       <c r="T11" t="n">
-        <v>0.457</v>
+        <v>-0.1025</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4169</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.702</v>
+        <v>-0.5068</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.702</v>
+        <v>-0.5068</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1643</v>
+        <v>-3.3636</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5311</v>
+        <v>-2.1803</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6333</v>
+        <v>-1.1834</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3069</v>
+        <v>-3.0053</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7269</v>
+        <v>-3.034</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4199</v>
+        <v>0.0286</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6947</v>
+        <v>-1.532</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7622</v>
+        <v>-1.6571</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0674</v>
+        <v>0.125</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6122</v>
+        <v>-1.4733</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9647</v>
+        <v>-1.3769</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3525</v>
+        <v>-0.0964</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4931</v>
+        <v>0.5438</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1637</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.3187</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6471</v>
+        <v>-1.4518</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6471</v>
+        <v>-1.7738</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3298</v>
+        <v>-3.4973</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7692</v>
+        <v>-0.9615</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5606</v>
+        <v>-2.5358</v>
       </c>
       <c r="G13" t="n">
         <v>-3.4572</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8582</v>
+        <v>0.6906</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2255</v>
+        <v>1.0332</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3674</v>
+        <v>-0.3426</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6471</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.9446</v>
+        <v>-5.3905</v>
       </c>
       <c r="E14" t="n">
         <v>-4.7175</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2271</v>
+        <v>-0.673</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1883</v>
@@ -1546,13 +1546,13 @@
         <v>2.3823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1683</v>
+        <v>-0.6142</v>
       </c>
       <c r="T14" t="n">
         <v>-0.552</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3837</v>
+        <v>-0.0622</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4726</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-10.7384</v>
+        <v>-9.5152</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.418799999999999</v>
+        <v>-7.4433</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3196</v>
+        <v>-2.0719</v>
       </c>
       <c r="G15" t="n">
         <v>-10.3508</v>
@@ -1624,13 +1624,13 @@
         <v>2.5656</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2473</v>
+        <v>-0.0241</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5158</v>
+        <v>0.4597</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7315</v>
+        <v>-0.4838</v>
       </c>
       <c r="V15" t="n">
         <v>0.1267</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.3103</v>
+        <v>-28.7597</v>
       </c>
       <c r="E16" t="n">
-        <v>-18.803</v>
+        <v>-18.2528</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.5073</v>
+        <v>-10.5074</v>
       </c>
       <c r="G16" t="n">
         <v>-23.8936</v>
@@ -1672,7 +1672,7 @@
         <v>-18.9262</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.9676</v>
+        <v>-4.967599999999999</v>
       </c>
       <c r="J16" t="n">
         <v>-12.3824</v>
@@ -1693,7 +1693,7 @@
         <v>1.2808</v>
       </c>
       <c r="P16" t="n">
-        <v>3.665099999999999</v>
+        <v>3.6651</v>
       </c>
       <c r="Q16" t="n">
         <v>-14.6606</v>
@@ -1702,16 +1702,16 @@
         <v>18.3256</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1920999999999999</v>
+        <v>0.3583999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>4.7401</v>
+        <v>5.2905</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.9323</v>
+        <v>-4.9322</v>
       </c>
       <c r="V16" t="n">
-        <v>-8.889600000000002</v>
+        <v>-8.8896</v>
       </c>
       <c r="W16" t="n">
         <v>3.4998</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8813</v>
+        <v>6.0052</v>
       </c>
       <c r="E17" t="n">
-        <v>5.7318</v>
+        <v>5.3472</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1495</v>
+        <v>0.658</v>
       </c>
       <c r="G17" t="n">
         <v>3.8486</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5403</v>
+        <v>-0.4165</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5664</v>
+        <v>0.1818</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1067</v>
+        <v>-0.5982</v>
       </c>
       <c r="V17" t="n">
         <v>3.4894</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3252</v>
+        <v>5.2358</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2312</v>
+        <v>2.7119</v>
       </c>
       <c r="F18" t="n">
-        <v>2.094</v>
+        <v>2.5238</v>
       </c>
       <c r="G18" t="n">
         <v>3.5128</v>
@@ -1858,13 +1858,13 @@
         <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0201</v>
+        <v>-0.1095</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7157</v>
+        <v>-0.2349</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3045</v>
+        <v>0.1254</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.0222</v>
+        <v>4.511</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6011</v>
+        <v>1.5732</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4211</v>
+        <v>2.9378</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3294</v>
+        <v>1.8804</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5507</v>
+        <v>3.1755</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7788</v>
+        <v>-1.2951</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.8505</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5294</v>
+        <v>2.6903</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0417</v>
+        <v>-1.8397</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7584</v>
+        <v>1.0299</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0213</v>
+        <v>0.4852</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7371</v>
+        <v>0.5446</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4416</v>
+        <v>-0.0683</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9517</v>
+        <v>0.0396</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4899</v>
+        <v>-0.1079</v>
       </c>
       <c r="V19" t="n">
-        <v>2.5339</v>
+        <v>1.5993</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9109</v>
+        <v>1.5993</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.9928</v>
+        <v>3.4335</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7078</v>
+        <v>1.4088</v>
       </c>
       <c r="F20" t="n">
-        <v>2.285</v>
+        <v>2.0247</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8804</v>
+        <v>1.3294</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1755</v>
+        <v>0.5507</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2951</v>
+        <v>0.7788</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8505</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6903</v>
+        <v>0.5294</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8397</v>
+        <v>0.0417</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0299</v>
+        <v>0.7584</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4852</v>
+        <v>0.0213</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5446</v>
+        <v>0.7371</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0995</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5864</v>
+        <v>0.8529</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8258</v>
+        <v>0.7594</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7607</v>
+        <v>0.0935</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5993</v>
+        <v>2.5339</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5993</v>
+        <v>1.9109</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.7598</v>
+        <v>3.2378</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3095</v>
+        <v>1.0057</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4503</v>
+        <v>2.2321</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1039</v>
+        <v>4.7623</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9789</v>
+        <v>1.8419</v>
       </c>
       <c r="I21" t="n">
-        <v>0.125</v>
+        <v>2.9204</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0252</v>
+        <v>1.8152</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.1116</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09320000000000001</v>
+        <v>1.9269</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0787</v>
+        <v>2.9471</v>
       </c>
       <c r="N21" t="n">
-        <v>1.0469</v>
+        <v>1.9535</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0318</v>
+        <v>0.9935</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5498</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1061</v>
+        <v>-0.0585</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2006</v>
+        <v>0.6723</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0945</v>
+        <v>-0.7308</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4767</v>
+        <v>3.2274</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3034</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7801</v>
+        <v>2.5333</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9055</v>
+        <v>2.1039</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2934</v>
+        <v>1.9789</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6121</v>
+        <v>0.125</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6589</v>
+        <v>1.0252</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5914</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0674</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2466</v>
+        <v>1.0787</v>
       </c>
       <c r="N22" t="n">
-        <v>0.702</v>
+        <v>1.0469</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5446</v>
+        <v>0.0318</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>0.121</v>
+        <v>0.5737</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1297</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2507</v>
+        <v>-0.0115</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.0749</v>
+        <v>2.5538</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9725</v>
+        <v>-0.1111</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1024</v>
+        <v>2.6649</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1078</v>
+        <v>2.9055</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1047</v>
+        <v>2.2934</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0031</v>
+        <v>0.6121</v>
       </c>
       <c r="J23" t="n">
-        <v>0.351</v>
+        <v>1.6589</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3094</v>
+        <v>1.5914</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0417</v>
+        <v>0.0674</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7567</v>
+        <v>1.2466</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2047</v>
+        <v>0.702</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9614</v>
+        <v>0.5446</v>
       </c>
       <c r="P23" t="n">
-        <v>1.0995</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1895</v>
+        <v>0.1981</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6214</v>
+        <v>0.0626</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4319</v>
+        <v>0.1355</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8537</v>
+        <v>2.1608</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.052</v>
+        <v>0.8763</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9057</v>
+        <v>1.2845</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7623</v>
+        <v>1.1078</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8419</v>
+        <v>0.1047</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9204</v>
+        <v>1.0031</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8152</v>
+        <v>0.351</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1116</v>
+        <v>0.3094</v>
       </c>
       <c r="L24" t="n">
-        <v>1.9269</v>
+        <v>0.0417</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9471</v>
+        <v>0.7567</v>
       </c>
       <c r="N24" t="n">
-        <v>1.9535</v>
+        <v>-0.2047</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9935</v>
+        <v>0.9614</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4425</v>
+        <v>0.2754</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3854</v>
+        <v>0.5253</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0572</v>
+        <v>-0.2498</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W24" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.8367</v>
+        <v>0.9502</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6405</v>
+        <v>0.9502</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4771</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6076</v>
+        <v>0.9502</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3703</v>
+        <v>0.3251</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2373</v>
+        <v>0.6251</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.688</v>
+        <v>0.9502</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.7714</v>
+        <v>0.3251</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0833</v>
+        <v>0.6251</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0804</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.4011</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3207</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5656</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4759</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1787</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2972</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. ALMONACID RUBIO</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1688</v>
+        <v>0.3462</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0163</v>
+        <v>-1.9866</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1851</v>
+        <v>2.3328</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8078</v>
+        <v>-0.6076</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1572</v>
+        <v>-0.3703</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6506</v>
+        <v>-0.2373</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1684</v>
+        <v>-1.688</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1268</v>
+        <v>-1.7714</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0417</v>
+        <v>0.0833</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6394</v>
+        <v>1.0804</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0305</v>
+        <v>1.4011</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6089</v>
+        <v>-0.3207</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.2828</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5498</v>
+        <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6438</v>
+        <v>0.9855</v>
       </c>
       <c r="T26" t="n">
-        <v>1.6478</v>
+        <v>0.8326</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.004</v>
+        <v>0.1529</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,31 +2515,31 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9502</v>
+        <v>0.3251</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9502</v>
+        <v>0.3251</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9502</v>
+        <v>0.3251</v>
       </c>
       <c r="H27" t="n">
         <v>0.3251</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6251</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9502</v>
+        <v>0.3251</v>
       </c>
       <c r="K27" t="n">
         <v>0.3251</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6251</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5201</v>
+        <v>0.0277</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9038</v>
+        <v>1.1346</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3837</v>
+        <v>-1.1069</v>
       </c>
       <c r="G28" t="n">
         <v>0.9738</v>
@@ -2638,13 +2638,13 @@
         <v>1.0995</v>
       </c>
       <c r="S28" t="n">
-        <v>0.9415</v>
+        <v>0.4491</v>
       </c>
       <c r="T28" t="n">
-        <v>1.5928</v>
+        <v>0.8235</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.6513</v>
+        <v>-0.3744</v>
       </c>
       <c r="V28" t="n">
         <v>-1.5785</v>
@@ -2659,7 +2659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>A. ALMONACID RUBIO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,58 +2671,58 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3251</v>
+        <v>-0.0302</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3251</v>
+        <v>-1.1702</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.1399</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3251</v>
+        <v>0.8078</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3251</v>
+        <v>0.1572</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.6506</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3251</v>
+        <v>0.1684</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3251</v>
+        <v>0.1268</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.6394</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.0305</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>0.6089</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>0.4448</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>0.494</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>-0.0492</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.8771</v>
+        <v>-0.1098</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.2135</v>
+        <v>-2.2519</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3364</v>
+        <v>2.1422</v>
       </c>
       <c r="G30" t="n">
         <v>-0.0062</v>
@@ -2794,13 +2794,13 @@
         <v>1.4661</v>
       </c>
       <c r="S30" t="n">
-        <v>-2.1378</v>
+        <v>-0.3705</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.1908</v>
       </c>
       <c r="U30" t="n">
-        <v>-1.3671</v>
+        <v>-0.5613</v>
       </c>
       <c r="V30" t="n">
         <v>0.6335</v>
@@ -2827,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>29.3104</v>
+        <v>31.8745</v>
       </c>
       <c r="E31" t="n">
         <v>10.5073</v>
       </c>
       <c r="F31" t="n">
-        <v>18.803</v>
+        <v>21.3671</v>
       </c>
       <c r="G31" t="n">
         <v>23.8938</v>
@@ -2842,7 +2842,7 @@
         <v>18.9262</v>
       </c>
       <c r="I31" t="n">
-        <v>4.967699999999999</v>
+        <v>4.967700000000001</v>
       </c>
       <c r="J31" t="n">
         <v>11.5112</v>
@@ -2851,7 +2851,7 @@
         <v>12.792</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.2805</v>
+        <v>-1.280499999999999</v>
       </c>
       <c r="M31" t="n">
         <v>12.3825</v>
@@ -2872,13 +2872,13 @@
         <v>14.6606</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1923000000000008</v>
+        <v>2.7562</v>
       </c>
       <c r="T31" t="n">
-        <v>4.9321</v>
+        <v>4.9322</v>
       </c>
       <c r="U31" t="n">
-        <v>-4.7401</v>
+        <v>-2.1758</v>
       </c>
       <c r="V31" t="n">
         <v>8.8896</v>
